--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92572043314</v>
+        <v>46157.93110610395</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110610395</v>
+        <v>46157.93178788997</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178788997</v>
+        <v>46157.93403596792</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93403596792</v>
+        <v>46157.9372160049</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372160049</v>
+        <v>46158.28219563193</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219563193</v>
+        <v>46158.29694444839</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29694444839</v>
+        <v>46158.29819031773</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29819031773</v>
+        <v>46158.33390662689</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33390662689</v>
+        <v>46158.36860383383</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36860383383</v>
+        <v>46158.37291105934</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
